--- a/tests/fixtures/budgeting/cash_sample.xlsx
+++ b/tests/fixtures/budgeting/cash_sample.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -484,17 +484,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lasten avaruusaiheinen pyöräilykypärä Torista</t>
+          <t>Test item</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yksityishenkilö</t>
+          <t>Kioski</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-01-20</t>
         </is>
       </c>
     </row>
